--- a/assets/constructions/examples/ctd_ds2.xlsx
+++ b/assets/constructions/examples/ctd_ds2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,11 +609,36 @@
           <t>hand</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A3387-6</t>
+          <t>A3387-10.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -633,11 +658,11 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
@@ -662,7 +687,7 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -670,23 +695,23 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>120</v>
       </c>
       <c r="V2" t="n">
-        <v>1.73</v>
+        <v>2.94</v>
       </c>
       <c r="W2" t="n">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="X2" t="n">
-        <v>80.27</v>
+        <v>115.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Z2" t="n">
         <v>3</v>
@@ -714,7 +739,7 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -725,13 +750,24 @@
       <c r="AJ2" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>KNO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TDG533A12000 WN10HD</t>
+          <t>TDG532A14000 WN10HD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -741,7 +777,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TDG533A</t>
+          <t>TDG532A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -751,7 +787,7 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -759,10 +795,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583</v>
+        <v>4.286</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -776,7 +812,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>TDG533A</t>
+          <t>TDG532A</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -794,7 +830,7 @@
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -809,16 +845,16 @@
         <v>130</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="W3" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="X3" t="n">
-        <v>138.2</v>
+        <v>120.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -844,7 +880,7 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-14</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -855,60 +891,57 @@
       <c r="AJ3" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TDG532A06000 WN10HD</t>
+          <t>A3387-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TDG532A</t>
+          <t>A3387</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>KNO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>IT9-IT10</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>35</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.833</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>h6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>WN10HD</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>TDG532A</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -916,15 +949,15 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>DIN 6535</t>
+          <t>DIN 6537 L</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -932,25 +965,27 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>2.89</v>
       </c>
       <c r="W4" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="X4" t="n">
-        <v>80.59999999999999</v>
+        <v>100.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
@@ -958,7 +993,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2018/Достижения RU</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -968,13 +1003,13 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>m7</t>
+          <t>k6</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -985,13 +1020,24 @@
       <c r="AJ4" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>KNO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A3387-19.5</t>
+          <t>A3387-6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1011,11 +1057,11 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -1040,7 +1086,7 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1048,23 +1094,23 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
         <v>120</v>
       </c>
       <c r="V5" t="n">
-        <v>5.63</v>
+        <v>1.73</v>
       </c>
       <c r="W5" t="n">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="X5" t="n">
-        <v>147.37</v>
+        <v>80.27</v>
       </c>
       <c r="Y5" t="n">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="Z5" t="n">
         <v>3</v>
@@ -1092,7 +1138,7 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1103,13 +1149,24 @@
       <c r="AJ5" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>KNO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TDG532A04217 WN10HD</t>
+          <t>TDG533A10000 WN10HD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1119,7 +1176,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TDG532A</t>
+          <t>TDG533A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1129,7 +1186,7 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4.217</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1137,10 +1194,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="I6" t="n">
-        <v>6.877</v>
+        <v>6.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1154,7 +1211,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>TDG532A</t>
+          <t>TDG533A</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1172,7 +1229,7 @@
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1180,23 +1237,23 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>130</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="W6" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="X6" t="n">
-        <v>73</v>
+        <v>119.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1222,7 +1279,7 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1233,6 +1290,17 @@
       <c r="AJ6" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
